--- a/wcd_experiments/full_param_grid_lesmis_summary.xlsx
+++ b/wcd_experiments/full_param_grid_lesmis_summary.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>full_param_grid_lesmis_a0.5_T08_h032_rho0.050_lr0.01_lam0.000100_bs16_ep600</t>
+          <t>full_param_grid_lesmis_a0.5_T06_h032_rho0.050_lr0.02_lam0.000330_bs16_ep600</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,7 +526,7 @@
         <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>32</v>
@@ -535,10 +535,10 @@
         <v>0.05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001</v>
+        <v>0.00033</v>
       </c>
       <c r="J2" t="n">
         <v>600</v>
@@ -556,13 +556,13 @@
         <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4886131766805505</v>
+        <v>0.415867043426533</v>
       </c>
       <c r="Q2" t="n">
-        <v>114.8251435000002</v>
+        <v>160.5575204999986</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
